--- a/templates/template_import_data_restorations.xlsx
+++ b/templates/template_import_data_restorations.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\repos\GanSoft\gansoft-resx\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB72464F-515B-40E7-9E4B-0FFEABB46906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75BF0A1-B1C6-40F6-ABF7-D4E4ED3360FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PesosCorporales" sheetId="1" r:id="rId1"/>
+    <sheet name="Restauraciones" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
